--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7142857142857143</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6971830985915493</v>
+        <v>0.7112676056338029</v>
       </c>
       <c r="D2">
-        <v>0.3233082706766917</v>
+        <v>0.3059701492537313</v>
       </c>
       <c r="E2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
